--- a/templates/filled-examples/FILLED_SALES_COMBINED.xlsx
+++ b/templates/filled-examples/FILLED_SALES_COMBINED.xlsx
@@ -8,14 +8,15 @@
     <sheet sheetId="2" name="BM" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="EBAY" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="ONBUY" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="README" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="TEMU" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="README" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="147">
   <si>
     <t>Date</t>
   </si>
@@ -306,6 +307,45 @@
   </si>
   <si>
     <t>350900000000020</t>
+  </si>
+  <si>
+    <t>Commission VAT</t>
+  </si>
+  <si>
+    <t>P. VAT</t>
+  </si>
+  <si>
+    <t>Acc</t>
+  </si>
+  <si>
+    <t>Total VAT</t>
+  </si>
+  <si>
+    <t>Total VAT NTP</t>
+  </si>
+  <si>
+    <t>TEMU-9020</t>
+  </si>
+  <si>
+    <t>350900000000021</t>
+  </si>
+  <si>
+    <t>TEMU-9021</t>
+  </si>
+  <si>
+    <t>350900000000022</t>
+  </si>
+  <si>
+    <t>TEMU-9022</t>
+  </si>
+  <si>
+    <t>350900000000023</t>
+  </si>
+  <si>
+    <t>TEMU-9023</t>
+  </si>
+  <si>
+    <t>350900000000024</t>
   </si>
   <si>
     <t>SALES REPORT — upload template</t>
@@ -1758,6 +1798,229 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="6" width="16" customWidth="1"/>
+    <col min="7" max="9" width="12" customWidth="1"/>
+    <col min="10" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>200</v>
+      </c>
+      <c r="H2">
+        <v>296</v>
+      </c>
+      <c r="K2">
+        <v>12.7</v>
+      </c>
+      <c r="L2">
+        <v>2.54</v>
+      </c>
+      <c r="M2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>207.25</v>
+      </c>
+      <c r="H3">
+        <v>306.01</v>
+      </c>
+      <c r="K3">
+        <v>15.73</v>
+      </c>
+      <c r="L3">
+        <v>3.15</v>
+      </c>
+      <c r="M3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>214.5</v>
+      </c>
+      <c r="H4">
+        <v>316.01</v>
+      </c>
+      <c r="K4">
+        <v>20.72</v>
+      </c>
+      <c r="L4">
+        <v>4.14</v>
+      </c>
+      <c r="M4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>221.75</v>
+      </c>
+      <c r="H5">
+        <v>326.02</v>
+      </c>
+      <c r="K5">
+        <v>25.09</v>
+      </c>
+      <c r="L5">
+        <v>5.02</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:S1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
@@ -1772,60 +2035,60 @@
   <sheetData>
     <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1833,13 +2096,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1847,13 +2110,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1861,13 +2124,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1875,27 +2138,27 @@
         <v>4</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1903,13 +2166,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1917,13 +2180,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1931,27 +2194,27 @@
         <v>47</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1959,27 +2222,27 @@
         <v>14</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
